--- a/backend/data/financials_by_company/1572.HK.xlsx
+++ b/backend/data/financials_by_company/1572.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV5"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,195 +662,121 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-50750</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D2" t="n">
-        <v>9251000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-203000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-203000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4523000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>796000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>53749000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>9048000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>8252000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1229000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>36000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1265000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>4675250</v>
-      </c>
-      <c r="P2" t="n">
-        <v>4523000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>58321000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>1686538000</v>
+        <v>1678000000</v>
       </c>
       <c r="S2" t="n">
-        <v>1686538000</v>
+        <v>1678000000</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0027</v>
+        <v>0.0151</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="V2" t="n">
-        <v>4523000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>4523000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>4523000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4523000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>4523000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3693000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8216000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-5593000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-203000</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>203000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1229000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>36000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1265000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>13023000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>4572000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>796000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>796000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2904000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2904000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>17595000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>53749000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>71344000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>71344000</v>
-      </c>
+        <v>0.0151</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>-56000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>5489000</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>8439000</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>572192.809071</v>
+        <v>575893.906941</v>
       </c>
       <c r="C3" t="n">
-        <v>0.331898</v>
+        <v>0.334822</v>
       </c>
       <c r="D3" t="n">
-        <v>15380000</v>
+        <v>20790000</v>
       </c>
       <c r="E3" t="n">
-        <v>1724000</v>
+        <v>1720000</v>
       </c>
       <c r="F3" t="n">
-        <v>1724000</v>
+        <v>1720000</v>
       </c>
       <c r="G3" t="n">
-        <v>11019000</v>
+        <v>14596000</v>
       </c>
       <c r="H3" t="n">
-        <v>575000</v>
+        <v>438000</v>
       </c>
       <c r="I3" t="n">
-        <v>37855000</v>
+        <v>3198000</v>
       </c>
       <c r="J3" t="n">
-        <v>17104000</v>
+        <v>22510000</v>
       </c>
       <c r="K3" t="n">
-        <v>16529000</v>
+        <v>22072000</v>
       </c>
       <c r="L3" t="n">
-        <v>2067000</v>
+        <v>2702000</v>
       </c>
       <c r="M3" t="n">
-        <v>36000</v>
+        <v>129000</v>
       </c>
       <c r="N3" t="n">
-        <v>2103000</v>
+        <v>2831000</v>
       </c>
       <c r="O3" t="n">
-        <v>9867192.809071001</v>
+        <v>13451893.906941</v>
       </c>
       <c r="P3" t="n">
-        <v>11019000</v>
+        <v>14596000</v>
       </c>
       <c r="Q3" t="n">
-        <v>40561000</v>
+        <v>3646000</v>
       </c>
       <c r="R3" t="n">
         <v>1678000000</v>
@@ -859,138 +785,144 @@
         <v>1678000000</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0066</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0066</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>11019000</v>
+        <v>14596000</v>
       </c>
       <c r="W3" t="n">
-        <v>11019000</v>
+        <v>14596000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>11019000</v>
+        <v>14596000</v>
       </c>
       <c r="Z3" t="n">
-        <v>11019000</v>
+        <v>14596000</v>
       </c>
       <c r="AA3" t="n">
-        <v>11019000</v>
+        <v>14596000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5474000</v>
+        <v>7347000</v>
       </c>
       <c r="AC3" t="n">
-        <v>16493000</v>
+        <v>21943000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-6351000</v>
+        <v>-5456000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1724000</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>1720000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-69000</v>
+      </c>
       <c r="AG3" t="n">
-        <v>-1724000</v>
+        <v>-1651000</v>
       </c>
       <c r="AH3" t="n">
-        <v>2067000</v>
+        <v>2702000</v>
       </c>
       <c r="AI3" t="n">
-        <v>36000</v>
+        <v>129000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2103000</v>
+        <v>2831000</v>
       </c>
       <c r="AK3" t="n">
-        <v>19181000</v>
+        <v>23692000</v>
       </c>
       <c r="AL3" t="n">
-        <v>2706000</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>448000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>614000</v>
+      </c>
       <c r="AN3" t="n">
-        <v>575000</v>
+        <v>438000</v>
       </c>
       <c r="AO3" t="n">
-        <v>575000</v>
+        <v>438000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1165000</v>
+        <v>10000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1165000</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>6874000</v>
+      </c>
       <c r="AS3" t="n">
-        <v>21887000</v>
+        <v>24140000</v>
       </c>
       <c r="AT3" t="n">
-        <v>37855000</v>
+        <v>3198000</v>
       </c>
       <c r="AU3" t="n">
-        <v>59742000</v>
+        <v>27338000</v>
       </c>
       <c r="AV3" t="n">
-        <v>59742000</v>
+        <v>27338000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>575893.906941</v>
+        <v>572192.809071</v>
       </c>
       <c r="C4" t="n">
-        <v>0.334822</v>
+        <v>0.331898</v>
       </c>
       <c r="D4" t="n">
-        <v>20790000</v>
+        <v>15380000</v>
       </c>
       <c r="E4" t="n">
-        <v>1720000</v>
+        <v>1724000</v>
       </c>
       <c r="F4" t="n">
-        <v>1720000</v>
+        <v>1724000</v>
       </c>
       <c r="G4" t="n">
-        <v>14596000</v>
+        <v>11019000</v>
       </c>
       <c r="H4" t="n">
-        <v>438000</v>
+        <v>575000</v>
       </c>
       <c r="I4" t="n">
-        <v>3198000</v>
+        <v>37855000</v>
       </c>
       <c r="J4" t="n">
-        <v>22510000</v>
+        <v>17104000</v>
       </c>
       <c r="K4" t="n">
-        <v>22072000</v>
+        <v>16529000</v>
       </c>
       <c r="L4" t="n">
-        <v>2702000</v>
+        <v>2067000</v>
       </c>
       <c r="M4" t="n">
-        <v>129000</v>
+        <v>36000</v>
       </c>
       <c r="N4" t="n">
-        <v>2831000</v>
+        <v>2103000</v>
       </c>
       <c r="O4" t="n">
-        <v>13451893.906941</v>
+        <v>9867192.809071001</v>
       </c>
       <c r="P4" t="n">
-        <v>14596000</v>
+        <v>11019000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3646000</v>
+        <v>40561000</v>
       </c>
       <c r="R4" t="n">
         <v>1678000000</v>
@@ -999,225 +931,361 @@
         <v>1678000000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="U4" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="V4" t="n">
-        <v>14596000</v>
+        <v>11019000</v>
       </c>
       <c r="W4" t="n">
-        <v>14596000</v>
+        <v>11019000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>14596000</v>
+        <v>11019000</v>
       </c>
       <c r="Z4" t="n">
-        <v>14596000</v>
+        <v>11019000</v>
       </c>
       <c r="AA4" t="n">
-        <v>14596000</v>
+        <v>11019000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7347000</v>
+        <v>5474000</v>
       </c>
       <c r="AC4" t="n">
-        <v>21943000</v>
+        <v>16493000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-5456000</v>
+        <v>-6351000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1720000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-69000</v>
-      </c>
+        <v>1724000</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>-1651000</v>
+        <v>-1724000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2702000</v>
+        <v>2067000</v>
       </c>
       <c r="AI4" t="n">
-        <v>129000</v>
+        <v>36000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2831000</v>
+        <v>2103000</v>
       </c>
       <c r="AK4" t="n">
-        <v>23692000</v>
+        <v>19181000</v>
       </c>
       <c r="AL4" t="n">
-        <v>448000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>614000</v>
-      </c>
+        <v>2706000</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>438000</v>
+        <v>575000</v>
       </c>
       <c r="AO4" t="n">
-        <v>438000</v>
+        <v>575000</v>
       </c>
       <c r="AP4" t="n">
-        <v>10000</v>
+        <v>1165000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>6874000</v>
-      </c>
+        <v>1165000</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>24140000</v>
+        <v>21887000</v>
       </c>
       <c r="AT4" t="n">
-        <v>3198000</v>
+        <v>37855000</v>
       </c>
       <c r="AU4" t="n">
-        <v>27338000</v>
+        <v>59742000</v>
       </c>
       <c r="AV4" t="n">
-        <v>27338000</v>
+        <v>59742000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>15477.089872</v>
+        <v>-50750</v>
       </c>
       <c r="C5" t="n">
-        <v>0.276377</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>35829000</v>
+        <v>9251000</v>
       </c>
       <c r="E5" t="n">
-        <v>56000</v>
+        <v>-203000</v>
       </c>
       <c r="F5" t="n">
-        <v>56000</v>
+        <v>-203000</v>
       </c>
       <c r="G5" t="n">
-        <v>25363000</v>
+        <v>4523000</v>
       </c>
       <c r="H5" t="n">
-        <v>653000</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>796000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>53749000</v>
+      </c>
       <c r="J5" t="n">
-        <v>35885000</v>
+        <v>9048000</v>
       </c>
       <c r="K5" t="n">
-        <v>35232000</v>
+        <v>8252000</v>
       </c>
       <c r="L5" t="n">
-        <v>2837000</v>
+        <v>1229000</v>
       </c>
       <c r="M5" t="n">
-        <v>182000</v>
+        <v>36000</v>
       </c>
       <c r="N5" t="n">
-        <v>3019000</v>
+        <v>1265000</v>
       </c>
       <c r="O5" t="n">
-        <v>25322477.089872</v>
+        <v>4675250</v>
       </c>
       <c r="P5" t="n">
-        <v>25363000</v>
+        <v>4523000</v>
       </c>
       <c r="Q5" t="n">
-        <v>13928000</v>
+        <v>58321000</v>
       </c>
       <c r="R5" t="n">
-        <v>1678000000</v>
+        <v>1686538000</v>
       </c>
       <c r="S5" t="n">
-        <v>1678000000</v>
+        <v>1686538000</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0151</v>
+        <v>0.0027</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0151</v>
+        <v>0.0027</v>
       </c>
       <c r="V5" t="n">
-        <v>25363000</v>
+        <v>4523000</v>
       </c>
       <c r="W5" t="n">
-        <v>25363000</v>
+        <v>4523000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>25363000</v>
+        <v>4523000</v>
       </c>
       <c r="Z5" t="n">
-        <v>25363000</v>
+        <v>4523000</v>
       </c>
       <c r="AA5" t="n">
-        <v>25363000</v>
+        <v>4523000</v>
       </c>
       <c r="AB5" t="n">
-        <v>9687000</v>
+        <v>3693000</v>
       </c>
       <c r="AC5" t="n">
-        <v>35050000</v>
+        <v>8216000</v>
       </c>
       <c r="AD5" t="n">
-        <v>175000</v>
+        <v>-5593000</v>
       </c>
       <c r="AE5" t="n">
-        <v>56000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-56000</v>
-      </c>
+        <v>-203000</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>2949000</v>
+        <v>203000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2837000</v>
+        <v>1229000</v>
       </c>
       <c r="AI5" t="n">
-        <v>182000</v>
+        <v>36000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3019000</v>
+        <v>1265000</v>
       </c>
       <c r="AK5" t="n">
-        <v>28968000</v>
+        <v>13023000</v>
       </c>
       <c r="AL5" t="n">
-        <v>13928000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>5489000</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
+        <v>4572000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="n">
+        <v>796000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>796000</v>
+      </c>
       <c r="AP5" t="n">
-        <v>8439000</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="n">
-        <v>8439000</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
+        <v>2904000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2904000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>17595000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>53749000</v>
+      </c>
       <c r="AU5" t="n">
-        <v>42896000</v>
+        <v>71344000</v>
       </c>
       <c r="AV5" t="n">
-        <v>42896000</v>
+        <v>71344000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-186750</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3303000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-747000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-747000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-488000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>985000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>121537000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2556000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1571000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>655000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>22000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>677000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>72250</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-488000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>126349000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>-488000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-488000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-488000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-488000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-488000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2037000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1549000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-6081000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-747000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>96000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>651000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>655000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>22000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>677000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>7301000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4812000</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>985000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>985000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2786000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2905000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-119000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>12113000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>121537000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>133650000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>133650000</v>
       </c>
     </row>
   </sheetData>
@@ -1231,7 +1299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV5"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1473,149 +1541,67 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1690500000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1690500000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7708000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1110279000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1117522000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1108409000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1110279000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>465000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1110279000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1110279000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1110279000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1110279000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>641794000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>199999000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>14793000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>14793000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>24900000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>186000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>186000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>5560000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>435000</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>24714000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>7708000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>465000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>7243000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>12524000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>11319000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1205000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1135179000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2056000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1123000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>933000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-1026000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1959000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="n">
-        <v>543000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1416000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1133123000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>32000000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>32000000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>447266000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>287000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>653570000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>653570000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>653570000</v>
-      </c>
+        <v>435000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="n">
+        <v>1478000</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1678000000</v>
@@ -1624,38 +1610,38 @@
         <v>1678000000</v>
       </c>
       <c r="D3" t="n">
-        <v>8249000</v>
+        <v>7563000</v>
       </c>
       <c r="E3" t="n">
-        <v>1104595000</v>
+        <v>1093656000</v>
       </c>
       <c r="F3" t="n">
-        <v>1111749000</v>
+        <v>1100784000</v>
       </c>
       <c r="G3" t="n">
-        <v>1102449000</v>
+        <v>1091481000</v>
       </c>
       <c r="H3" t="n">
-        <v>1104595000</v>
+        <v>1093656000</v>
       </c>
       <c r="I3" t="n">
-        <v>1095000</v>
+        <v>435000</v>
       </c>
       <c r="J3" t="n">
-        <v>1104595000</v>
+        <v>1093656000</v>
       </c>
       <c r="K3" t="n">
-        <v>1104595000</v>
+        <v>1093656000</v>
       </c>
       <c r="L3" t="n">
-        <v>1104595000</v>
+        <v>1093656000</v>
       </c>
       <c r="M3" t="n">
-        <v>1104595000</v>
+        <v>1093656000</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>638224000</v>
+        <v>628342000</v>
       </c>
       <c r="P3" t="n">
         <v>198794000</v>
@@ -1667,97 +1653,99 @@
         <v>14679000</v>
       </c>
       <c r="S3" t="n">
-        <v>27206000</v>
+        <v>14890000</v>
       </c>
       <c r="T3" t="n">
-        <v>811000</v>
+        <v>223000</v>
       </c>
       <c r="U3" t="n">
-        <v>346000</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>465000</v>
+        <v>223000</v>
       </c>
       <c r="W3" t="n">
-        <v>465000</v>
+        <v>223000</v>
       </c>
       <c r="X3" t="n">
-        <v>26395000</v>
+        <v>14667000</v>
       </c>
       <c r="Y3" t="n">
-        <v>7784000</v>
+        <v>7340000</v>
       </c>
       <c r="Z3" t="n">
-        <v>630000</v>
+        <v>212000</v>
       </c>
       <c r="AA3" t="n">
-        <v>7154000</v>
+        <v>7128000</v>
       </c>
       <c r="AB3" t="n">
-        <v>13166000</v>
+        <v>2025000</v>
       </c>
       <c r="AC3" t="n">
-        <v>8093000</v>
+        <v>305000</v>
       </c>
       <c r="AD3" t="n">
-        <v>5073000</v>
+        <v>1720000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1131801000</v>
+        <v>1108546000</v>
       </c>
       <c r="AF3" t="n">
-        <v>2957000</v>
+        <v>2398000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1230000</v>
+        <v>1387000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1727000</v>
+        <v>1011000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-869000</v>
+        <v>-713000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2596000</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+        <v>1724000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1011000</v>
+      </c>
       <c r="AL3" t="n">
         <v>541000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2055000</v>
+        <v>1183000</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>1128844000</v>
+        <v>1106148000</v>
       </c>
       <c r="AP3" t="n">
-        <v>10600000</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10600000</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>422426000</v>
+        <v>493642000</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="AT3" t="n">
-        <v>695818000</v>
+        <v>612418000</v>
       </c>
       <c r="AU3" t="n">
-        <v>695818000</v>
+        <v>612418000</v>
       </c>
       <c r="AV3" t="n">
-        <v>695818000</v>
+        <v>612418000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1678000000</v>
@@ -1766,38 +1754,38 @@
         <v>1678000000</v>
       </c>
       <c r="D4" t="n">
-        <v>7563000</v>
+        <v>8249000</v>
       </c>
       <c r="E4" t="n">
-        <v>1093656000</v>
+        <v>1104595000</v>
       </c>
       <c r="F4" t="n">
-        <v>1100784000</v>
+        <v>1111749000</v>
       </c>
       <c r="G4" t="n">
-        <v>1091481000</v>
+        <v>1102449000</v>
       </c>
       <c r="H4" t="n">
-        <v>1093656000</v>
+        <v>1104595000</v>
       </c>
       <c r="I4" t="n">
-        <v>435000</v>
+        <v>1095000</v>
       </c>
       <c r="J4" t="n">
-        <v>1093656000</v>
+        <v>1104595000</v>
       </c>
       <c r="K4" t="n">
-        <v>1093656000</v>
+        <v>1104595000</v>
       </c>
       <c r="L4" t="n">
-        <v>1093656000</v>
+        <v>1104595000</v>
       </c>
       <c r="M4" t="n">
-        <v>1093656000</v>
+        <v>1104595000</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>628342000</v>
+        <v>638224000</v>
       </c>
       <c r="P4" t="n">
         <v>198794000</v>
@@ -1809,234 +1797,372 @@
         <v>14679000</v>
       </c>
       <c r="S4" t="n">
-        <v>14890000</v>
+        <v>27206000</v>
       </c>
       <c r="T4" t="n">
-        <v>223000</v>
+        <v>811000</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>346000</v>
       </c>
       <c r="V4" t="n">
-        <v>223000</v>
+        <v>465000</v>
       </c>
       <c r="W4" t="n">
-        <v>223000</v>
+        <v>465000</v>
       </c>
       <c r="X4" t="n">
-        <v>14667000</v>
+        <v>26395000</v>
       </c>
       <c r="Y4" t="n">
-        <v>7340000</v>
+        <v>7784000</v>
       </c>
       <c r="Z4" t="n">
-        <v>212000</v>
+        <v>630000</v>
       </c>
       <c r="AA4" t="n">
-        <v>7128000</v>
+        <v>7154000</v>
       </c>
       <c r="AB4" t="n">
-        <v>2025000</v>
+        <v>13166000</v>
       </c>
       <c r="AC4" t="n">
-        <v>305000</v>
+        <v>8093000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1720000</v>
+        <v>5073000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1108546000</v>
+        <v>1131801000</v>
       </c>
       <c r="AF4" t="n">
-        <v>2398000</v>
+        <v>2957000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1387000</v>
+        <v>1230000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1011000</v>
+        <v>1727000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-713000</v>
+        <v>-869000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1724000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1011000</v>
-      </c>
+        <v>2596000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
         <v>541000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1183000</v>
+        <v>2055000</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1106148000</v>
+        <v>1128844000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>10600000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>10600000</v>
       </c>
       <c r="AR4" t="n">
-        <v>493642000</v>
+        <v>422426000</v>
       </c>
       <c r="AS4" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>612418000</v>
+        <v>695818000</v>
       </c>
       <c r="AU4" t="n">
-        <v>612418000</v>
+        <v>695818000</v>
       </c>
       <c r="AV4" t="n">
-        <v>612418000</v>
+        <v>695818000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1678000000</v>
+        <v>1690500000</v>
       </c>
       <c r="C5" t="n">
-        <v>1678000000</v>
+        <v>1690500000</v>
       </c>
       <c r="D5" t="n">
-        <v>7126000</v>
+        <v>7708000</v>
       </c>
       <c r="E5" t="n">
-        <v>1079109000</v>
+        <v>1110279000</v>
       </c>
       <c r="F5" t="n">
-        <v>1085536000</v>
+        <v>1117522000</v>
       </c>
       <c r="G5" t="n">
-        <v>1074153000</v>
+        <v>1108409000</v>
       </c>
       <c r="H5" t="n">
-        <v>1079109000</v>
+        <v>1110279000</v>
       </c>
       <c r="I5" t="n">
-        <v>699000</v>
+        <v>465000</v>
       </c>
       <c r="J5" t="n">
-        <v>1079109000</v>
+        <v>1110279000</v>
       </c>
       <c r="K5" t="n">
-        <v>1079109000</v>
+        <v>1110279000</v>
       </c>
       <c r="L5" t="n">
-        <v>1079109000</v>
+        <v>1110279000</v>
       </c>
       <c r="M5" t="n">
-        <v>1079109000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5560000</v>
-      </c>
+        <v>1110279000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>610267000</v>
+        <v>641794000</v>
       </c>
       <c r="P5" t="n">
-        <v>198794000</v>
+        <v>199999000</v>
       </c>
       <c r="Q5" t="n">
-        <v>14679000</v>
+        <v>14793000</v>
       </c>
       <c r="R5" t="n">
-        <v>14679000</v>
+        <v>14793000</v>
       </c>
       <c r="S5" t="n">
-        <v>13955000</v>
+        <v>24900000</v>
       </c>
       <c r="T5" t="n">
-        <v>435000</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>186000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>186000</v>
+      </c>
       <c r="V5" t="n">
-        <v>435000</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>435000</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>13520000</v>
+        <v>24714000</v>
       </c>
       <c r="Y5" t="n">
-        <v>6691000</v>
+        <v>7708000</v>
       </c>
       <c r="Z5" t="n">
-        <v>264000</v>
+        <v>465000</v>
       </c>
       <c r="AA5" t="n">
-        <v>6427000</v>
+        <v>7243000</v>
       </c>
       <c r="AB5" t="n">
-        <v>4018000</v>
+        <v>12524000</v>
       </c>
       <c r="AC5" t="n">
-        <v>25000</v>
+        <v>11319000</v>
       </c>
       <c r="AD5" t="n">
-        <v>3993000</v>
+        <v>1205000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1093064000</v>
+        <v>1135179000</v>
       </c>
       <c r="AF5" t="n">
-        <v>5391000</v>
+        <v>2056000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1800000</v>
+        <v>1123000</v>
       </c>
       <c r="AH5" t="n">
-        <v>1478000</v>
+        <v>933000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1143000</v>
+        <v>-1026000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2621000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1478000</v>
-      </c>
+        <v>1959000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>1174000</v>
+        <v>543000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1447000</v>
+        <v>1416000</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>1087673000</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
+        <v>1133123000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>32000000</v>
+      </c>
       <c r="AR5" t="n">
-        <v>370620000</v>
+        <v>447266000</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>287000</v>
       </c>
       <c r="AT5" t="n">
-        <v>717053000</v>
+        <v>653570000</v>
       </c>
       <c r="AU5" t="n">
-        <v>717053000</v>
+        <v>653570000</v>
       </c>
       <c r="AV5" t="n">
-        <v>717053000</v>
+        <v>653570000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1690500000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1690500000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>28608000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1109988000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1138243000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1107849000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1109988000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>353000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1109988000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1109988000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1109988000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1109988000</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>641089000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>199999000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>14793000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>14793000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>37249000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>174000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>174000</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>37075000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>28608000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>353000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>28255000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>4858000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1940000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2918000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1147237000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2313000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1258000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1055000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-487000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1542000</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>348000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1194000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1144924000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>382600000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>382600000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>499614000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>262710000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>262710000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>262710000</v>
       </c>
     </row>
   </sheetData>
@@ -2050,7 +2176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,377 +2345,489 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Repayment Of Debt</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Long Term Debt Payments</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Gain Loss On Sale Of Business</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-47804000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="n">
-        <v>1364000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>6388000</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>653570000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>695818000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-42250000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4289000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3636000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1364000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1364000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>1263000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1265000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-2000</v>
-      </c>
+        <v>-127000</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>6388000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6388000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6388000</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-47802000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-5907000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-49995000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-3552000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>-21400000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-25043000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-1229000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>796000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>796000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>114000</v>
-      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>-1081000</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>8216000</v>
-      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>75612000</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
+        <v>-109722000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>695818000</v>
+        <v>612418000</v>
       </c>
       <c r="G3" t="n">
-        <v>612418000</v>
+        <v>717053000</v>
       </c>
       <c r="H3" t="n">
         <v>3000</v>
       </c>
       <c r="I3" t="n">
-        <v>83397000</v>
+        <v>-104638000</v>
       </c>
       <c r="J3" t="n">
-        <v>5682000</v>
+        <v>-58000</v>
       </c>
       <c r="K3" t="n">
-        <v>6349000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+        <v>235000</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q3" t="n">
-        <v>2103000</v>
+        <v>5142000</v>
       </c>
       <c r="R3" t="n">
-        <v>2103000</v>
+        <v>2788000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>101000</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>101000</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>75612000</v>
+        <v>-109722000</v>
       </c>
       <c r="W3" t="n">
-        <v>-3491000</v>
+        <v>-9163000</v>
       </c>
       <c r="X3" t="n">
-        <v>65831000</v>
+        <v>-119002000</v>
       </c>
       <c r="Y3" t="n">
-        <v>3491000</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
+        <v>2361000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2361000</v>
+      </c>
       <c r="AA3" t="n">
-        <v>-10600000</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>72940000</v>
+        <v>-121363000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2067000</v>
+        <v>-2702000</v>
       </c>
       <c r="AD3" t="n">
-        <v>575000</v>
+        <v>438000</v>
       </c>
       <c r="AE3" t="n">
-        <v>575000</v>
+        <v>438000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-5000</v>
+        <v>484000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="AH3" t="n">
-        <v>16493000</v>
-      </c>
+        <v>21943000</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-109722000</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>75612000</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
+        <v>695818000</v>
+      </c>
+      <c r="G4" t="n">
         <v>612418000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>717053000</v>
       </c>
       <c r="H4" t="n">
         <v>3000</v>
       </c>
       <c r="I4" t="n">
-        <v>-104638000</v>
+        <v>83397000</v>
       </c>
       <c r="J4" t="n">
-        <v>-58000</v>
+        <v>5682000</v>
       </c>
       <c r="K4" t="n">
-        <v>235000</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
+        <v>6349000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>5142000</v>
+        <v>2103000</v>
       </c>
       <c r="R4" t="n">
-        <v>2788000</v>
+        <v>2103000</v>
       </c>
       <c r="S4" t="n">
-        <v>101000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>101000</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-109722000</v>
+        <v>75612000</v>
       </c>
       <c r="W4" t="n">
-        <v>-9163000</v>
+        <v>-3491000</v>
       </c>
       <c r="X4" t="n">
-        <v>-119002000</v>
+        <v>65831000</v>
       </c>
       <c r="Y4" t="n">
-        <v>2361000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2361000</v>
-      </c>
+        <v>3491000</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-10600000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-121363000</v>
+        <v>72940000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2702000</v>
+        <v>-2067000</v>
       </c>
       <c r="AD4" t="n">
-        <v>438000</v>
+        <v>575000</v>
       </c>
       <c r="AE4" t="n">
-        <v>438000</v>
+        <v>575000</v>
       </c>
       <c r="AF4" t="n">
-        <v>484000</v>
+        <v>-5000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-69000</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>21943000</v>
-      </c>
+        <v>16493000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-25595000</v>
+        <v>-47804000</v>
       </c>
       <c r="C5" t="n">
-        <v>6388000</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1364000</v>
+      </c>
       <c r="E5" t="n">
-        <v>-127000</v>
+        <v>-2000</v>
       </c>
       <c r="F5" t="n">
-        <v>717053000</v>
+        <v>653570000</v>
       </c>
       <c r="G5" t="n">
-        <v>827661000</v>
+        <v>695818000</v>
       </c>
       <c r="H5" t="n">
-        <v>-3000</v>
+        <v>2000</v>
       </c>
       <c r="I5" t="n">
-        <v>-110605000</v>
+        <v>-42250000</v>
       </c>
       <c r="J5" t="n">
-        <v>-86060000</v>
+        <v>4289000</v>
       </c>
       <c r="K5" t="n">
-        <v>-91859000</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>3636000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1364000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1364000</v>
+      </c>
       <c r="N5" t="n">
-        <v>6388000</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>6388000</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>6388000</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>923000</v>
+        <v>1263000</v>
       </c>
       <c r="R5" t="n">
-        <v>2949000</v>
+        <v>1265000</v>
       </c>
       <c r="S5" t="n">
-        <v>48000</v>
+        <v>-2000</v>
       </c>
       <c r="T5" t="n">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-127000</v>
+        <v>-2000</v>
       </c>
       <c r="V5" t="n">
-        <v>-25468000</v>
+        <v>-47802000</v>
       </c>
       <c r="W5" t="n">
-        <v>-9958000</v>
+        <v>-5907000</v>
       </c>
       <c r="X5" t="n">
-        <v>-48371000</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="n">
-        <v>-1081000</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
+        <v>-49995000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-3552000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>-21400000</v>
+      </c>
       <c r="AB5" t="n">
-        <v>-47290000</v>
+        <v>-25043000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2837000</v>
+        <v>-1229000</v>
       </c>
       <c r="AD5" t="n">
-        <v>653000</v>
+        <v>796000</v>
       </c>
       <c r="AE5" t="n">
-        <v>653000</v>
+        <v>796000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-2898000</v>
+        <v>114000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-56000</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>35050000</v>
+        <v>8216000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-401248000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10648000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-499000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>262710000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>653570000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-50000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-390810000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9745000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>58000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10523000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>10523000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10648000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>194000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>677000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-483000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>16000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-499000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-400749000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-1865000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-401767000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1832000</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>-350600000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-52999000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>59000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>985000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>985000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-457000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>78000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1549000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-125000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-125000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>18000</v>
       </c>
     </row>
   </sheetData>
@@ -3109,187 +3347,187 @@
       </c>
       <c r="CW1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>shortName</t>
         </is>
       </c>
       <c r="EH1" t="inlineStr">
@@ -3364,7 +3602,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Xiaobing  Chen', 'age': 34, 'title': 'Executive Co-Chairman', 'yearBorn': 1991, 'fiscalYear': 2025, 'totalPay': 8109, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhijun  Fan', 'age': 59, 'title': 'General Manager', 'yearBorn': 1966, 'fiscalYear': 2025, 'totalPay': 377652, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bin  Zhang', 'age': 50, 'title': 'Chief Operations Officer', 'yearBorn': 1975, 'fiscalYear': 2025, 'totalPay': 208519, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Changsheng  Liu', 'age': 49, 'title': 'Executive Director', 'yearBorn': 1976, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ke  Xiong', 'age': 36, 'title': 'Executive Director', 'yearBorn': 1989, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bo  Wu', 'age': 37, 'title': 'Executive Director', 'yearBorn': 1988, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kam Ming  Ng', 'age': 39, 'title': 'Company Secretary', 'yearBorn': 1986, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Xiaobing  Chen', 'age': 34, 'title': 'Executive Co-Chairman', 'yearBorn': 1991, 'fiscalYear': 2025, 'totalPay': 8103, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhijun  Fan', 'age': 59, 'title': 'General Manager', 'yearBorn': 1966, 'fiscalYear': 2025, 'totalPay': 377351, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bin  Zhang', 'age': 50, 'title': 'Chief Operations Officer', 'yearBorn': 1975, 'fiscalYear': 2025, 'totalPay': 208353, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Changsheng  Liu', 'age': 49, 'title': 'Executive Director', 'yearBorn': 1976, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ke  Xiong', 'age': 36, 'title': 'Executive Director', 'yearBorn': 1989, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bo  Wu', 'age': 37, 'title': 'Executive Director', 'yearBorn': 1988, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kam Ming  Ng', 'age': 39, 'title': 'Company Secretary', 'yearBorn': 1986, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -3382,28 +3620,28 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>0.094</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.09</v>
+        <v>0.083</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="V2" t="n">
-        <v>0.094</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>0.094</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>0.09</v>
+        <v>0.083</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.094</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1562198400</v>
@@ -3412,28 +3650,28 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.559</v>
+        <v>1.568</v>
       </c>
       <c r="AD2" t="n">
-        <v>704000</v>
+        <v>216000</v>
       </c>
       <c r="AE2" t="n">
-        <v>704000</v>
+        <v>216000</v>
       </c>
       <c r="AF2" t="n">
-        <v>860733</v>
+        <v>775864</v>
       </c>
       <c r="AG2" t="n">
-        <v>608000</v>
+        <v>265200</v>
       </c>
       <c r="AH2" t="n">
-        <v>608000</v>
+        <v>265200</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.093</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -3442,10 +3680,10 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>155526000</v>
+        <v>143692496</v>
       </c>
       <c r="AN2" t="n">
-        <v>158907000</v>
+        <v>143692500</v>
       </c>
       <c r="AO2" t="n">
         <v>0.075</v>
@@ -3460,13 +3698,13 @@
         <v>0.057</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.1636813</v>
+        <v>1.0751402</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.091</v>
+        <v>0.09086</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.09811</v>
+        <v>0.09658</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -3483,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-78576000</v>
+        <v>-90409504</v>
       </c>
       <c r="BA2" t="n">
         <v>-0.00365</v>
@@ -3504,10 +3742,10 @@
         <v>1690500000</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.7608992</v>
+        <v>0.7604894</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.12090958</v>
+        <v>0.11177013</v>
       </c>
       <c r="BI2" t="n">
         <v>1767139200</v>
@@ -3525,16 +3763,16 @@
         <v>-0</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0.588</v>
+        <v>-0.676</v>
       </c>
       <c r="BO2" t="n">
-        <v>-10.505</v>
+        <v>-12.087</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.03296709</v>
+        <v>0.037037015</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BR2" t="n">
         <v>0.01</v>
@@ -3548,7 +3786,7 @@
         </is>
       </c>
       <c r="BU2" t="n">
-        <v>0.092</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
@@ -3647,140 +3885,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CW2" t="n">
-        <v>-2.127656</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>0.092</v>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>CHINA ART FIN</t>
+        </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>PRE</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
           <t>China Art Financial Holdings Limited</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="CZ2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>-0.005860001</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>-0.06449483</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>-0.011579998</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>-0.11990058</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1782115193</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>finmb_407516589</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DB2" t="n">
-        <v>1780387186</v>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>finmb_407516589</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DG2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
+      <c r="DP2" t="n">
+        <v>1.1904786</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="DR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
         <v>1478568600000</v>
       </c>
-      <c r="DL2" t="n">
-        <v>-0.0019999966</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>0.086 - 0.094</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.001000002</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>0.078 - 0.085</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DO2" t="n">
-        <v>860733</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.016999997</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.22666661</v>
-      </c>
-      <c r="DR2" t="inlineStr">
+      <c r="DX2" t="n">
+        <v>775864</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.009999998</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.1333333</v>
+      </c>
+      <c r="EA2" t="inlineStr">
         <is>
           <t>0.075 - 0.142</t>
         </is>
       </c>
-      <c r="DS2" t="n">
-        <v>-0.050000004</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.3521127</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>3.296709</v>
-      </c>
-      <c r="DV2" t="n">
+      <c r="EB2" t="n">
+        <v>-0.057000004</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.40140846</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>3.7037015</v>
+      </c>
+      <c r="EE2" t="n">
         <v>1743164183</v>
       </c>
-      <c r="DW2" t="n">
+      <c r="EF2" t="n">
         <v>1743164183</v>
       </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.001000002</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.010989034</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.0061099976</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.06227701</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>CHINA ART FIN</t>
-        </is>
+      <c r="EG2" t="b">
+        <v>0</v>
       </c>
       <c r="EH2" t="inlineStr"/>
     </row>
